--- a/campus-tests/SIT Master/Programming/set4_medium.xlsx
+++ b/campus-tests/SIT Master/Programming/set4_medium.xlsx
@@ -540,7 +540,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t xml:space="preserve">olleh </t>
+          <t>hell</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
